--- a/data/sars/alaska/tables/Alaska_2002_Appendix2.xlsx
+++ b/data/sars/alaska/tables/Alaska_2002_Appendix2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/alaska/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E99EDAB-5E02-C648-8172-8AA2254DDD07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C0FE89-AFE6-1548-BA0E-80C5B8B99F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5140" yWindow="5460" windowWidth="27640" windowHeight="16940" xr2:uid="{C9E0D584-D559-7744-9D6D-49A3FFA7DB02}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="67">
   <si>
     <t>Alaska</t>
   </si>
@@ -215,6 +215,12 @@
   </si>
   <si>
     <t>W.U. S.</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> yes</t>
   </si>
 </sst>
 </file>
@@ -369,7 +375,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -547,6 +553,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -710,7 +722,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -722,6 +734,18 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1099,7 +1123,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9635E785-F461-D846-9F26-C8E9B21B97C4}">
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44.5" style="1" customWidth="1"/>
@@ -1107,7 +1131,7 @@
     <col min="3" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>49</v>
       </c>
@@ -1151,10 +1175,13 @@
         <v>62</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
@@ -1185,301 +1212,322 @@
       <c r="N2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="1">
+      <c r="B3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
         <v>0.06</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="5">
         <v>0.5</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L3" s="1">
-        <v>1</v>
-      </c>
-      <c r="M3" s="2">
+      <c r="K3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="6">
         <v>6788</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="O3" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="6">
         <v>39258</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="5">
         <v>0.22900000000000001</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="5">
         <v>2</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1">
+      <c r="F4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5">
         <v>0.22900000000000001</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="6">
         <v>32453</v>
       </c>
-      <c r="I4" s="1">
+      <c r="I4" s="5">
         <v>0.02</v>
       </c>
-      <c r="J4" s="1">
-        <v>1</v>
-      </c>
-      <c r="K4" s="1">
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
         <v>649</v>
       </c>
-      <c r="L4" s="1">
-        <v>0</v>
-      </c>
-      <c r="M4" s="1">
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
         <v>177</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="N4" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+      <c r="O4" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="6">
         <v>3710</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1">
+      <c r="D5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5">
         <v>3.09</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="2">
+      <c r="F5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="6">
         <v>3710</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I5" s="5">
         <v>0.02</v>
       </c>
-      <c r="J5" s="1">
-        <v>1</v>
-      </c>
-      <c r="K5" s="1">
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
         <v>74</v>
       </c>
-      <c r="L5" s="1">
-        <v>0</v>
-      </c>
-      <c r="M5" s="1">
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
         <v>60</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="N5" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="O5" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="6">
         <v>18142</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="5">
         <v>0.24</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="5">
         <v>3.09</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1">
+      <c r="F6" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5">
         <v>0.24</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="6">
         <v>14898</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I6" s="5">
         <v>0.02</v>
       </c>
-      <c r="J6" s="1">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1">
+      <c r="J6" s="5">
+        <v>1</v>
+      </c>
+      <c r="K6" s="5">
         <v>298</v>
       </c>
-      <c r="L6" s="1">
-        <v>1</v>
-      </c>
-      <c r="M6" s="1">
+      <c r="L6" s="5">
+        <v>1</v>
+      </c>
+      <c r="M6" s="5">
         <v>164</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="N6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="O6" s="3" t="s">
+      <c r="O6" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="P6" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="6">
         <v>1888</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="D7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5">
         <v>3.09</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1">
+      <c r="F7" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
         <v>0.2</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="6">
         <v>1619</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I7" s="5">
         <v>0.02</v>
       </c>
-      <c r="J7" s="1">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1">
+      <c r="J7" s="5">
+        <v>1</v>
+      </c>
+      <c r="K7" s="5">
         <v>32</v>
       </c>
-      <c r="L7" s="1">
-        <v>1</v>
-      </c>
-      <c r="M7" s="1">
+      <c r="L7" s="5">
+        <v>1</v>
+      </c>
+      <c r="M7" s="5">
         <v>15</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="N7" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="O7" s="3" t="s">
+      <c r="O7" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="P7" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="5">
         <v>435</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="5">
         <v>0.23</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="5">
         <v>0.23</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="5">
         <v>360</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8" s="5">
         <v>0.02</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="5">
         <v>0.3</v>
       </c>
-      <c r="K8" s="1">
+      <c r="K8" s="5">
         <v>2.2000000000000002</v>
       </c>
-      <c r="L8" s="1">
-        <v>0</v>
-      </c>
-      <c r="M8" s="1">
-        <v>0</v>
-      </c>
-      <c r="N8" s="1" t="s">
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="O8" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="6">
         <v>8200</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="5">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="5">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="6">
         <v>7738</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="5">
         <v>0.02</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="5">
         <v>0.5</v>
       </c>
-      <c r="K9" s="1">
+      <c r="K9" s="5">
         <v>77</v>
       </c>
-      <c r="L9" s="1">
+      <c r="L9" s="5">
         <v>0.2</v>
       </c>
-      <c r="M9" s="1">
+      <c r="M9" s="5">
         <v>52</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="N9" s="5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O9" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>29</v>
       </c>
@@ -1511,7 +1559,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>30</v>
       </c>
@@ -1549,77 +1597,83 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="1">
+      <c r="C12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5">
         <v>0.02</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="5">
         <v>0.1</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L12" s="1">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1">
-        <v>0</v>
-      </c>
-      <c r="N12" s="1" t="s">
+      <c r="K12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
+      <c r="O12" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="6">
         <v>26635</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" s="5">
         <v>0.10059999999999999</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="5">
         <v>0.10059999999999999</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="6">
         <v>24477</v>
       </c>
-      <c r="I13" s="1">
+      <c r="I13" s="5">
         <v>2.35E-2</v>
       </c>
-      <c r="J13" s="1">
-        <v>1</v>
-      </c>
-      <c r="K13" s="1">
+      <c r="J13" s="5">
+        <v>1</v>
+      </c>
+      <c r="K13" s="5">
         <v>575</v>
       </c>
-      <c r="L13" s="1">
+      <c r="L13" s="5">
         <v>8.9</v>
       </c>
-      <c r="M13" s="1">
+      <c r="M13" s="5">
         <v>97</v>
       </c>
-      <c r="N13" s="1" t="s">
+      <c r="N13" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>31</v>
       </c>
@@ -1662,11 +1716,11 @@
       <c r="N14" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>31</v>
       </c>
@@ -1710,7 +1764,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
@@ -1754,7 +1808,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>17</v>
       </c>
@@ -1798,7 +1852,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -1842,7 +1896,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -1885,266 +1939,287 @@
       <c r="N19" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="O19" s="4"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+      <c r="P19" s="4"/>
+    </row>
+    <row r="20" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="5">
         <v>394</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" s="5">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" s="5">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H20" s="5">
         <v>367</v>
       </c>
-      <c r="I20" s="1">
+      <c r="I20" s="5">
         <v>0.02</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J20" s="5">
         <v>0.1</v>
       </c>
-      <c r="K20" s="1">
+      <c r="K20" s="5">
         <v>0.7</v>
       </c>
-      <c r="L20" s="1">
+      <c r="L20" s="5">
         <v>0.6</v>
       </c>
-      <c r="M20" s="1">
-        <v>0</v>
-      </c>
-      <c r="N20" s="1" t="s">
+      <c r="M20" s="5">
+        <v>0</v>
+      </c>
+      <c r="N20" s="5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
+      <c r="O20" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="6">
         <v>4005</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="5">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" s="5">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="6">
         <v>3698</v>
       </c>
-      <c r="I21" s="1">
+      <c r="I21" s="5">
         <v>0.02</v>
       </c>
-      <c r="J21" s="1">
+      <c r="J21" s="5">
         <v>0.1</v>
       </c>
-      <c r="K21" s="1">
+      <c r="K21" s="5">
         <v>7.4</v>
       </c>
-      <c r="L21" s="1">
+      <c r="L21" s="5">
         <v>4.0999999999999996</v>
       </c>
-      <c r="M21" s="1">
-        <v>0</v>
-      </c>
-      <c r="N21" s="1" t="s">
+      <c r="M21" s="5">
+        <v>0</v>
+      </c>
+      <c r="N21" s="5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
+      <c r="O21" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="5">
         <v>723</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G22" s="1" t="s">
+      <c r="D22" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H22" s="1">
+      <c r="H22" s="5">
         <v>723</v>
       </c>
-      <c r="I22" s="1">
+      <c r="I22" s="5">
         <v>0.02</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="5">
         <v>0.5</v>
       </c>
-      <c r="K22" s="1">
+      <c r="K22" s="5">
         <v>7.2</v>
       </c>
-      <c r="L22" s="1">
+      <c r="L22" s="5">
         <v>1.4</v>
       </c>
-      <c r="M22" s="1">
-        <v>0</v>
-      </c>
-      <c r="N22" s="1" t="s">
+      <c r="M22" s="5">
+        <v>0</v>
+      </c>
+      <c r="N22" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="1" t="s">
+      <c r="O22" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="P22" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="5">
         <v>346</v>
       </c>
-      <c r="D23" s="1">
-        <v>1</v>
-      </c>
-      <c r="H23" s="1">
+      <c r="D23" s="5">
+        <v>1</v>
+      </c>
+      <c r="H23" s="5">
         <v>346</v>
       </c>
-      <c r="I23" s="1">
+      <c r="I23" s="5">
         <v>0.04</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J23" s="5">
         <v>0.04</v>
       </c>
-      <c r="K23" s="1">
+      <c r="K23" s="5">
         <v>2.8</v>
       </c>
-      <c r="L23" s="1">
+      <c r="L23" s="5">
         <v>0.6</v>
       </c>
-      <c r="M23" s="1">
-        <v>0</v>
-      </c>
-      <c r="N23" s="1" t="s">
+      <c r="M23" s="5">
+        <v>0</v>
+      </c>
+      <c r="N23" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
+      <c r="O23" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I24" s="1">
+      <c r="B24" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I24" s="5">
         <v>0.02</v>
       </c>
-      <c r="J24" s="1">
+      <c r="J24" s="5">
         <v>0.5</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L24" s="1">
-        <v>0</v>
-      </c>
-      <c r="M24" s="1">
-        <v>0</v>
-      </c>
-      <c r="N24" s="1" t="s">
+      <c r="K24" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L24" s="5">
+        <v>0</v>
+      </c>
+      <c r="M24" s="5">
+        <v>0</v>
+      </c>
+      <c r="N24" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
+      <c r="O24" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I25" s="1">
+      <c r="C25" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I25" s="5">
         <v>0.02</v>
       </c>
-      <c r="J25" s="1">
+      <c r="J25" s="5">
         <v>0.1</v>
       </c>
-      <c r="K25" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L25" s="1">
-        <v>0</v>
-      </c>
-      <c r="M25" s="1">
-        <v>0</v>
-      </c>
-      <c r="N25" s="1" t="s">
+      <c r="K25" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L25" s="5">
+        <v>0</v>
+      </c>
+      <c r="M25" s="5">
+        <v>0</v>
+      </c>
+      <c r="N25" s="5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
+      <c r="O25" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="6">
         <v>941756</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26" s="5">
         <v>4.4749999999999996</v>
       </c>
-      <c r="F26" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G26" s="1">
+      <c r="F26" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G26" s="5">
         <v>0.2</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26" s="6">
         <v>797112</v>
       </c>
-      <c r="I26" s="1">
+      <c r="I26" s="5">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="J26" s="1">
+      <c r="J26" s="5">
         <v>0.5</v>
       </c>
-      <c r="K26" s="2">
+      <c r="K26" s="6">
         <v>17138</v>
       </c>
-      <c r="L26" s="1">
+      <c r="L26" s="5">
         <v>15</v>
       </c>
-      <c r="M26" s="2">
+      <c r="M26" s="6">
         <v>1495</v>
       </c>
-      <c r="N26" s="1" t="s">
+      <c r="N26" s="5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O26" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>20</v>
       </c>
@@ -2176,7 +2251,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>21</v>
       </c>
@@ -2208,7 +2283,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>22</v>
       </c>
@@ -2240,7 +2315,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>23</v>
       </c>
@@ -2272,39 +2347,42 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
+    <row r="31" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="I31" s="1">
+      <c r="B31" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I31" s="5">
         <v>0.06</v>
       </c>
-      <c r="J31" s="1">
+      <c r="J31" s="5">
         <v>0.5</v>
       </c>
-      <c r="K31" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L31" s="1">
+      <c r="K31" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L31" s="5">
         <v>3</v>
       </c>
-      <c r="M31" s="2">
+      <c r="M31" s="6">
         <v>5265</v>
       </c>
-      <c r="N31" s="1" t="s">
+      <c r="N31" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>35</v>
       </c>
@@ -2336,73 +2414,79 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
+    <row r="33" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="6">
         <v>31028</v>
       </c>
-      <c r="H33" s="2">
+      <c r="H33" s="6">
         <v>31028</v>
       </c>
-      <c r="I33" s="1">
+      <c r="I33" s="5">
         <v>0.06</v>
       </c>
-      <c r="J33" s="1">
+      <c r="J33" s="5">
         <v>0.75</v>
       </c>
-      <c r="K33" s="2">
+      <c r="K33" s="6">
         <v>1396</v>
       </c>
-      <c r="L33" s="1">
+      <c r="L33" s="5">
         <v>3.4</v>
       </c>
-      <c r="M33" s="1">
-        <v>0</v>
-      </c>
-      <c r="N33" s="1" t="s">
+      <c r="M33" s="5">
+        <v>0</v>
+      </c>
+      <c r="N33" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="O33" s="3" t="s">
+      <c r="O33" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="P33" s="7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="6">
         <v>34595</v>
       </c>
-      <c r="H34" s="2">
+      <c r="H34" s="6">
         <v>34595</v>
       </c>
-      <c r="I34" s="1">
+      <c r="I34" s="5">
         <v>0.06</v>
       </c>
-      <c r="J34" s="1">
+      <c r="J34" s="5">
         <v>0.1</v>
       </c>
-      <c r="K34" s="2">
+      <c r="K34" s="6">
         <v>208</v>
       </c>
-      <c r="L34" s="1">
+      <c r="L34" s="5">
         <v>29.5</v>
       </c>
-      <c r="M34" s="1">
+      <c r="M34" s="5">
         <v>167.5</v>
       </c>
-      <c r="N34" s="1" t="s">
+      <c r="N34" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="O34" s="4"/>
+      <c r="O34" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="P34" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
